--- a/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49826</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58042</t>
+          <t>57696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92147</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>644186</t>
+          <t>645255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668017</t>
+          <t>668471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638929</t>
+          <t>639045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661639</t>
+          <t>662267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1290216</t>
+          <t>1292388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324321</t>
+          <t>1324667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54348</t>
+          <t>52051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59036</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93460</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119071</t>
+          <t>120757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167380</t>
+          <t>167826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>873868</t>
+          <t>874343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>905434</t>
+          <t>907731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>874933</t>
+          <t>875497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909357</t>
+          <t>908778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1760795</t>
+          <t>1760349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1809104</t>
+          <t>1807418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33645</t>
+          <t>33115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61316</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72987</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85899</t>
+          <t>86358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>127431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612496</t>
+          <t>613057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640167</t>
+          <t>640697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609626</t>
+          <t>608325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637766</t>
+          <t>637448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1231357</t>
+          <t>1228994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1270526</t>
+          <t>1270067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>53108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>83658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121863</t>
+          <t>121621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145737</t>
+          <t>145589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194836</t>
+          <t>192652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853955</t>
+          <t>856002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886069</t>
+          <t>886552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913701</t>
+          <t>913943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954293</t>
+          <t>953528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1780388</t>
+          <t>1782572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829487</t>
+          <t>1829635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189845</t>
+          <t>189776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>248188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>239778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307359</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448730</t>
+          <t>449897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>532442</t>
+          <t>534914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3019456</t>
+          <t>3019078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3077421</t>
+          <t>3077490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3067562</t>
+          <t>3071937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3133390</t>
+          <t>3135143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6109745</t>
+          <t>6107273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6193457</t>
+          <t>6192290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84023</t>
+          <t>84425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63228</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100476</t>
+          <t>96861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123719</t>
+          <t>124747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171580</t>
+          <t>172209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619446</t>
+          <t>619044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>652229</t>
+          <t>653292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>596574</t>
+          <t>600189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633822</t>
+          <t>633127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1228939</t>
+          <t>1228310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1276800</t>
+          <t>1275772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81340</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121743</t>
+          <t>123025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104630</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147852</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198614</t>
+          <t>195313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255277</t>
+          <t>255039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>894023</t>
+          <t>892741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>934426</t>
+          <t>934125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>884332</t>
+          <t>885205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927554</t>
+          <t>927629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1792673</t>
+          <t>1792911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1849336</t>
+          <t>1852637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>49565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81535</t>
+          <t>83047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60591</t>
+          <t>59300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97349</t>
+          <t>97167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118762</t>
+          <t>117490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167651</t>
+          <t>167571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676088</t>
+          <t>674576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>708363</t>
+          <t>708058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679825</t>
+          <t>680007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>716583</t>
+          <t>717874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1367146</t>
+          <t>1367226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1416035</t>
+          <t>1417307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75388</t>
+          <t>76467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116387</t>
+          <t>115841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108217</t>
+          <t>107869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151541</t>
+          <t>152093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195368</t>
+          <t>192319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256098</t>
+          <t>252513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830367</t>
+          <t>830913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871366</t>
+          <t>870287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898465</t>
+          <t>897913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>941789</t>
+          <t>942137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1740662</t>
+          <t>1744247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1801392</t>
+          <t>1804441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>291937</t>
+          <t>290109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365686</t>
+          <t>363057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>372104</t>
+          <t>371795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>450408</t>
+          <t>454340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>683949</t>
+          <t>684420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>785386</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3057926</t>
+          <t>3060555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3131675</t>
+          <t>3133503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3106006</t>
+          <t>3102074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3184310</t>
+          <t>3184619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6194641</t>
+          <t>6187418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6296078</t>
+          <t>6295607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47512</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>76699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101104</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144297</t>
+          <t>141061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600778</t>
+          <t>599952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>630565</t>
+          <t>630172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>594934</t>
+          <t>596140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>625327</t>
+          <t>626025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203342</t>
+          <t>1206578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246535</t>
+          <t>1249197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>53328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86704</t>
+          <t>86541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74502</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112192</t>
+          <t>111876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189607</t>
+          <t>191078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>928470</t>
+          <t>928633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>962760</t>
+          <t>961846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927840</t>
+          <t>928156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965530</t>
+          <t>968189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1865599</t>
+          <t>1864128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1918055</t>
+          <t>1918985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44776</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>66660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103331</t>
+          <t>105211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>705307</t>
+          <t>703908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729383</t>
+          <t>728216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711623</t>
+          <t>711814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>741986</t>
+          <t>742468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1427597</t>
+          <t>1425717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1464399</t>
+          <t>1464268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>63888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101302</t>
+          <t>98207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>82542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124615</t>
+          <t>124512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>156725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208493</t>
+          <t>211929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836265</t>
+          <t>839360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873006</t>
+          <t>873679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919164</t>
+          <t>919267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959440</t>
+          <t>961237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1772853</t>
+          <t>1769417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1823682</t>
+          <t>1824621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207562</t>
+          <t>206871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272160</t>
+          <t>269362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274838</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>343640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501359</t>
+          <t>500086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>591663</t>
+          <t>596343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3105464</t>
+          <t>3108262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3170062</t>
+          <t>3170753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3193951</t>
+          <t>3193856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3262658</t>
+          <t>3261798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6323456</t>
+          <t>6318776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6413760</t>
+          <t>6415033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>74892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107835</t>
+          <t>109259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111298</t>
+          <t>111678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160448</t>
+          <t>160636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211343</t>
+          <t>210579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>524500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>557877</t>
+          <t>558867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609234</t>
+          <t>608854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645865</t>
+          <t>645475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1142948</t>
+          <t>1143712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1193843</t>
+          <t>1193655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182639</t>
+          <t>180860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136120</t>
+          <t>136172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172579</t>
+          <t>172405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188535</t>
+          <t>190735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335774</t>
+          <t>335838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007987</t>
+          <t>1009766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1114524</t>
+          <t>1121927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>778838</t>
+          <t>779012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>815297</t>
+          <t>815245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1806268</t>
+          <t>1806204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1953507</t>
+          <t>1951307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88635</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129803</t>
+          <t>130608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129421</t>
+          <t>129761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>582321</t>
+          <t>642330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236134</t>
+          <t>238604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>877054</t>
+          <t>856856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568002</t>
+          <t>567197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609170</t>
+          <t>607382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>350124</t>
+          <t>290115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>803024</t>
+          <t>802684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>753196</t>
+          <t>773394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1394116</t>
+          <t>1391646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>88827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128455</t>
+          <t>129483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101293</t>
+          <t>100769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>148845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>200317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265788</t>
+          <t>262684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786448</t>
+          <t>785420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>825140</t>
+          <t>826076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945094</t>
+          <t>942447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>989999</t>
+          <t>990523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1740408</t>
+          <t>1743512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1805827</t>
+          <t>1805879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>351263</t>
+          <t>338505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>498687</t>
+          <t>500210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>499800</t>
+          <t>496321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1225374</t>
+          <t>1231422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>928987</t>
+          <t>927262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1976213</t>
+          <t>1857005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2938406</t>
+          <t>2936883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3085830</t>
+          <t>3098588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2470313</t>
+          <t>2464265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3195887</t>
+          <t>3199366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5156566</t>
+          <t>5275774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6203792</t>
+          <t>6205517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>49185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89975</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>645255</t>
+          <t>646171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668471</t>
+          <t>668716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639045</t>
+          <t>639166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>662267</t>
+          <t>660206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292388</t>
+          <t>1291079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324667</t>
+          <t>1324073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>52404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85439</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59615</t>
+          <t>58933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92896</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120757</t>
+          <t>121810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167826</t>
+          <t>168751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>874343</t>
+          <t>874463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>907731</t>
+          <t>907378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875497</t>
+          <t>873888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>908778</t>
+          <t>909460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1760349</t>
+          <t>1759424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1807418</t>
+          <t>1806365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>60499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45165</t>
+          <t>45386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74288</t>
+          <t>74089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86358</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127431</t>
+          <t>125558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613057</t>
+          <t>613313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640697</t>
+          <t>641580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608325</t>
+          <t>608524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>637227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228994</t>
+          <t>1230867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1270067</t>
+          <t>1271771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83658</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>82871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121621</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145589</t>
+          <t>146074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192652</t>
+          <t>196955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856002</t>
+          <t>856538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886552</t>
+          <t>886419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913943</t>
+          <t>912594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>953528</t>
+          <t>952693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1782572</t>
+          <t>1778269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829635</t>
+          <t>1829150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189776</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>248188</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239778</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>449897</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534914</t>
+          <t>532244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3019078</t>
+          <t>3016894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3077490</t>
+          <t>3078028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3071937</t>
+          <t>3068995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3135143</t>
+          <t>3130583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6107273</t>
+          <t>6109943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6192290</t>
+          <t>6193990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50177</t>
+          <t>51107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84425</t>
+          <t>83186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>62699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>97757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124747</t>
+          <t>122945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172209</t>
+          <t>170264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619044</t>
+          <t>620283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>653292</t>
+          <t>652362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600189</t>
+          <t>599293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633127</t>
+          <t>634351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1228310</t>
+          <t>1230255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1275772</t>
+          <t>1277574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>82455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123025</t>
+          <t>122680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104555</t>
+          <t>104809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146979</t>
+          <t>147261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195313</t>
+          <t>199964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>255734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>892741</t>
+          <t>893086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>934125</t>
+          <t>933311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>885205</t>
+          <t>884923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927629</t>
+          <t>927375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1792911</t>
+          <t>1792216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1852637</t>
+          <t>1847986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>49688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83047</t>
+          <t>83223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97167</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117490</t>
+          <t>118473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167571</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674576</t>
+          <t>674400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>708058</t>
+          <t>707935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680007</t>
+          <t>680707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717874</t>
+          <t>716157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1367226</t>
+          <t>1368649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1417307</t>
+          <t>1416324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76467</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>117297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107869</t>
+          <t>108428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152093</t>
+          <t>151533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192319</t>
+          <t>194058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252513</t>
+          <t>254147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830913</t>
+          <t>829457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870287</t>
+          <t>868332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>897913</t>
+          <t>898473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>942137</t>
+          <t>941578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1744247</t>
+          <t>1742613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1804441</t>
+          <t>1802702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>290109</t>
+          <t>291578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>363057</t>
+          <t>364317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371795</t>
+          <t>371725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>454340</t>
+          <t>453782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>684420</t>
+          <t>683989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>793306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3060555</t>
+          <t>3059295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3133503</t>
+          <t>3132034</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3102074</t>
+          <t>3102632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3184619</t>
+          <t>3184689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6187418</t>
+          <t>6186721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6295607</t>
+          <t>6296038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44628</t>
+          <t>42758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>73717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>76585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98442</t>
+          <t>100022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141061</t>
+          <t>141741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>599952</t>
+          <t>601083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>630172</t>
+          <t>632042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>596140</t>
+          <t>596254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>626025</t>
+          <t>625833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1206578</t>
+          <t>1205898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1249197</t>
+          <t>1247617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53328</t>
+          <t>53719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86541</t>
+          <t>87853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71843</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111876</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191078</t>
+          <t>188821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>928633</t>
+          <t>927321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>961846</t>
+          <t>961455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928156</t>
+          <t>925603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>968189</t>
+          <t>965030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864128</t>
+          <t>1866385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1918985</t>
+          <t>1920484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46175</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66660</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105211</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>703908</t>
+          <t>705808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728216</t>
+          <t>728231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711814</t>
+          <t>711297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742468</t>
+          <t>741981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1425717</t>
+          <t>1424852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1464268</t>
+          <t>1463407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63888</t>
+          <t>64786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98207</t>
+          <t>98889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>83511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124512</t>
+          <t>124556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156725</t>
+          <t>158149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211929</t>
+          <t>208997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839360</t>
+          <t>838678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873679</t>
+          <t>872781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919267</t>
+          <t>919223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961237</t>
+          <t>960268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1769417</t>
+          <t>1772349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824621</t>
+          <t>1823197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>206871</t>
+          <t>204528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269362</t>
+          <t>268352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343640</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>500086</t>
+          <t>501779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>596343</t>
+          <t>593632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3108262</t>
+          <t>3109272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3170753</t>
+          <t>3173096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3193856</t>
+          <t>3192128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3261798</t>
+          <t>3261719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6318776</t>
+          <t>6321487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6415033</t>
+          <t>6413340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90856</t>
+          <t>95127</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>78512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109259</t>
+          <t>113506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>95133</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75057</t>
+          <t>88783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111678</t>
+          <t>118512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>185989</t>
+          <t>197655</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160636</t>
+          <t>175260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210579</t>
+          <t>223212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>542903</t>
+          <t>593783</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>524500</t>
+          <t>575404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>558867</t>
+          <t>610398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>625399</t>
+          <t>626707</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>608854</t>
+          <t>610723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645475</t>
+          <t>640452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1168302</t>
+          <t>1220490</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143712</t>
+          <t>1194933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1193655</t>
+          <t>1242885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633759</t>
+          <t>688910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633759</t>
+          <t>688910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633759</t>
+          <t>688910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>720532</t>
+          <t>729235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>720532</t>
+          <t>729235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>720532</t>
+          <t>729235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1354291</t>
+          <t>1418145</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1354291</t>
+          <t>1418145</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1354291</t>
+          <t>1418145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>136024</t>
+          <t>147668</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68699</t>
+          <t>123167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180860</t>
+          <t>175146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152490</t>
+          <t>168879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136172</t>
+          <t>150155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172405</t>
+          <t>189981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>288513</t>
+          <t>316546</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190735</t>
+          <t>288441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335838</t>
+          <t>348025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1054602</t>
+          <t>898767</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009766</t>
+          <t>871289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121927</t>
+          <t>923268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>798927</t>
+          <t>894522</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>779012</t>
+          <t>873420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>815245</t>
+          <t>913246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1853529</t>
+          <t>1793289</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1806204</t>
+          <t>1761810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1951307</t>
+          <t>1821394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190626</t>
+          <t>1046435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190626</t>
+          <t>1046435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190626</t>
+          <t>1046435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>951417</t>
+          <t>1063401</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>951417</t>
+          <t>1063401</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>951417</t>
+          <t>1063401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2142042</t>
+          <t>2109835</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2142042</t>
+          <t>2109835</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2142042</t>
+          <t>2109835</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108216</t>
+          <t>121041</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>101629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130608</t>
+          <t>144594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>312354</t>
+          <t>130293</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129761</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>642330</t>
+          <t>153155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>420570</t>
+          <t>251334</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238604</t>
+          <t>223135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>856856</t>
+          <t>279461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>589589</t>
+          <t>671760</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567197</t>
+          <t>648207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>607382</t>
+          <t>691172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>620091</t>
+          <t>681011</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290115</t>
+          <t>658149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>802684</t>
+          <t>698782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1209680</t>
+          <t>1352771</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>773394</t>
+          <t>1324644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1391646</t>
+          <t>1380970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>697805</t>
+          <t>792801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>697805</t>
+          <t>792801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>697805</t>
+          <t>792801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932445</t>
+          <t>811304</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932445</t>
+          <t>811304</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932445</t>
+          <t>811304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1630250</t>
+          <t>1604105</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1630250</t>
+          <t>1604105</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1630250</t>
+          <t>1604105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>110874</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88827</t>
+          <t>92183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129483</t>
+          <t>132918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126650</t>
+          <t>137557</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100769</t>
+          <t>119029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148845</t>
+          <t>156708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>233760</t>
+          <t>248431</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200317</t>
+          <t>224675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262684</t>
+          <t>277131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>807793</t>
+          <t>866872</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>785420</t>
+          <t>844828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>826076</t>
+          <t>885563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>964642</t>
+          <t>977494</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942447</t>
+          <t>958343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>990523</t>
+          <t>996022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1772436</t>
+          <t>1844366</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1743512</t>
+          <t>1815666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1805879</t>
+          <t>1868122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>914903</t>
+          <t>977746</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>914903</t>
+          <t>977746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>914903</t>
+          <t>977746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091292</t>
+          <t>1115051</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091292</t>
+          <t>1115051</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091292</t>
+          <t>1115051</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2006196</t>
+          <t>2092797</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2006196</t>
+          <t>2092797</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2006196</t>
+          <t>2092797</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>338505</t>
+          <t>428364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500210</t>
+          <t>515490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>496321</t>
+          <t>503319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1231422</t>
+          <t>576475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>927262</t>
+          <t>957866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1857005</t>
+          <t>1073169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2994887</t>
+          <t>3031181</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2936883</t>
+          <t>2990402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3098588</t>
+          <t>3077528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3009059</t>
+          <t>3179733</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2464265</t>
+          <t>3142515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3199366</t>
+          <t>3215671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6003946</t>
+          <t>6210915</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5275774</t>
+          <t>6151713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6205517</t>
+          <t>6267016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
